--- a/test_doc/new_org/syllabus_6_english.xlsx
+++ b/test_doc/new_org/syllabus_6_english.xlsx
@@ -441,16 +441,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Prose: A Tale of Two Birds</t>
+          <t>Writing: Letters</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Reading and comprehension</t>
+          <t>Informal letters</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -461,26 +461,26 @@
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vocabulary</t>
+          <t>Formal letters</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Grammar: Nouns and Pronouns</t>
+          <t>Poetry: A House, A Home</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kinds of nouns</t>
+          <t>Recitation and meaning</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pronoun usage</t>
+          <t>Appreciation</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -501,12 +501,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Prose: The Friendly Mongoose</t>
+          <t>Grammar: Adjectives and Adverbs</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Reading and comprehension</t>
+          <t>Degrees of comparison</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -521,26 +521,26 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>Character discussion</t>
+          <t>Adverb placement</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Writing: Paragraphs</t>
+          <t>Prose: A Tale of Two Birds</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Structure of a paragraph</t>
+          <t>Reading and comprehension</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -551,26 +551,26 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>Guided writing</t>
+          <t>Vocabulary</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Poetry: A House, A Home</t>
+          <t>Prose: The Shepherd's Treasure</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Recitation and meaning</t>
+          <t>Reading and comprehension</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -581,26 +581,26 @@
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>Appreciation</t>
+          <t>Retelling</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Grammar: Verbs and Tenses</t>
+          <t>Poetry: The Kite</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Simple tenses</t>
+          <t>Recitation and meaning</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -611,26 +611,26 @@
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>Subject-verb agreement</t>
+          <t>Imagery</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Prose: The Shepherd's Treasure</t>
+          <t>Writing: Paragraphs</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Reading and comprehension</t>
+          <t>Structure of a paragraph</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -641,26 +641,26 @@
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>Retelling</t>
+          <t>Guided writing</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Writing: Letters</t>
+          <t>Prose: Flying Together</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Informal letters</t>
+          <t>Reading and comprehension</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -671,26 +671,26 @@
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>Formal letters</t>
+          <t>Story discussion</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Grammar: Adjectives and Adverbs</t>
+          <t>Prose: The Friendly Mongoose</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Degrees of comparison</t>
+          <t>Reading and comprehension</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -701,26 +701,26 @@
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>Adverb placement</t>
+          <t>Character discussion</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Poetry: The Kite</t>
+          <t>Grammar: Verbs and Tenses</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Recitation and meaning</t>
+          <t>Simple tenses</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>Imagery</t>
+          <t>Subject-verb agreement</t>
         </is>
       </c>
       <c r="C21" t="n">
